--- a/data/trans_camb/P1403-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1403-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,41</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,84</t>
+          <t>-0,32; 0,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,33</t>
+          <t>-0,31; 1,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,08</t>
+          <t>-0,22; 3,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; -0,17</t>
+          <t>-1,67; -0,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,32</t>
+          <t>-1,21; 0,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,31</t>
+          <t>-0,74; 2,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,13</t>
+          <t>-0,72; 0,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,54</t>
+          <t>-0,56; 0,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,92</t>
+          <t>-0,26; 1,83</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-73,23%</t>
+          <t>340,28%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>114,72%</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,6</t>
+          <t>-0,02; 1,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,3</t>
+          <t>0,1; 2,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,34</t>
+          <t>0,5; 4,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,63</t>
+          <t>-1,43; 1,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; -0,13</t>
+          <t>-2,46; -0,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,77</t>
+          <t>-1,8; 0,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,25</t>
+          <t>-0,36; 1,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,76</t>
+          <t>-0,71; 0,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,18</t>
+          <t>-0,25; 2,02</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>316,6%</t>
+          <t>660,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-37,64%</t>
+          <t>-37,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-60,39; —</t>
+          <t>-50,8; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,33; —</t>
+          <t>-45,97; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-79,16; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,61; 192,14</t>
+          <t>-66,13; 224,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 7,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,81; 105,83</t>
+          <t>-84,84; 124,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,94; 243,45</t>
+          <t>-34,6; 241,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,1; 164,17</t>
+          <t>-63,52; 168,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-51,59; 254,73</t>
+          <t>-31,35; 332,07</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,01</t>
+          <t>-2,12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,7</t>
+          <t>-0,16; 4,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,4</t>
+          <t>-1,59; 2,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,83</t>
+          <t>-1,54; 2,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,12</t>
+          <t>-2,88; 1,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,04</t>
+          <t>-3,87; 0,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,9; -0,08</t>
+          <t>-4,18; -0,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,91</t>
+          <t>-1,07; 1,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,5</t>
+          <t>-2,3; 0,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,72</t>
+          <t>-2,33; 0,61</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-45,17%</t>
+          <t>-47,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-19,83%</t>
+          <t>-19,98%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 158,65</t>
+          <t>-7,52; 182,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 109,02</t>
+          <t>-41,99; 103,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,35; 133,37</t>
+          <t>-39,19; 117,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,87; 37,63</t>
+          <t>-52,95; 47,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,22; 1,24</t>
+          <t>-69,96; 7,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,03; 1,48</t>
+          <t>-71,0; -6,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 63,32</t>
+          <t>-24,2; 63,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,22; 18,93</t>
+          <t>-48,56; 22,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,0; 21,0</t>
+          <t>-49,27; 20,03</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,85</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>1,82</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 2,07</t>
+          <t>-6,14; 1,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 3,94</t>
+          <t>-4,75; 3,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 4,17</t>
+          <t>-2,08; 6,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 6,16</t>
+          <t>-1,53; 6,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 1,16</t>
+          <t>-5,56; 1,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 5,57</t>
+          <t>-1,83; 4,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 3,13</t>
+          <t>-2,36; 3,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,46</t>
+          <t>-3,99; 1,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 3,39</t>
+          <t>-1,11; 4,53</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-13,32%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-1,04%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,96; 17,42</t>
+          <t>-38,39; 15,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 34,77</t>
+          <t>-30,23; 28,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,49; 32,13</t>
+          <t>-13,14; 53,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 66,89</t>
+          <t>-12,08; 71,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,83; 13,71</t>
+          <t>-42,28; 17,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 65,08</t>
+          <t>-13,66; 51,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 28,84</t>
+          <t>-17,48; 30,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,71; 13,23</t>
+          <t>-28,84; 13,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,49; 28,26</t>
+          <t>-7,88; 40,25</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,37</t>
+          <t>-2,27</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,29</t>
+          <t>-4,79</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,31</t>
+          <t>-3,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 11,14</t>
+          <t>-2,54; 10,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 0,65</t>
+          <t>-11,83; 0,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 3,92</t>
+          <t>-8,52; 3,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 14,65</t>
+          <t>0,23; 13,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 4,64</t>
+          <t>-7,66; 4,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 0,44</t>
+          <t>-10,04; 0,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,91</t>
+          <t>0,91; 10,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 0,93</t>
+          <t>-8,26; 0,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 0,81</t>
+          <t>-7,48; 0,37</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-4,42%</t>
+          <t>-7,36%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-16,75%</t>
+          <t>-15,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-10,59%</t>
+          <t>-11,32%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 41,18</t>
+          <t>-7,7; 37,71</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 2,7</t>
+          <t>-34,57; 3,65</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 14,47</t>
+          <t>-24,12; 11,3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3,5; 51,52</t>
+          <t>0,59; 48,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 16,31</t>
+          <t>-22,11; 15,78</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,26; 1,76</t>
+          <t>-28,31; 1,99</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,29; 38,13</t>
+          <t>2,57; 37,67</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 3,31</t>
+          <t>-24,55; 1,32</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 2,81</t>
+          <t>-21,54; 1,36</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7,61</t>
+          <t>6,91</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,63</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15,08</t>
+          <t>3,77</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,99; 21,91</t>
+          <t>4,95; 21,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 9,28</t>
+          <t>-4,84; 10,17</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,71; 14,96</t>
+          <t>-0,06; 13,63</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,75; 19,01</t>
+          <t>3,68; 18,57</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 7,93</t>
+          <t>-6,71; 7,92</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 42,84</t>
+          <t>-5,37; 7,83</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,53; 17,64</t>
+          <t>6,49; 17,69</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 6,32</t>
+          <t>-4,5; 6,81</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,22; 35,52</t>
+          <t>-0,68; 8,45</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>11,51; 62,16</t>
+          <t>11,16; 61,51</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 26,71</t>
+          <t>-11,45; 29,92</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1,58; 44,09</t>
+          <t>0,09; 40,63</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,4; 46,18</t>
+          <t>7,34; 43,9</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 19,01</t>
+          <t>-13,71; 18,53</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 103,42</t>
+          <t>-10,64; 19,09</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,98; 44,14</t>
+          <t>14,42; 44,89</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 16,09</t>
+          <t>-10,02; 17,29</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5,06; 87,0</t>
+          <t>-1,49; 21,23</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7,27</t>
+          <t>6,91</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,09</t>
+          <t>7,68</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7,64</t>
+          <t>7,24</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,67; 22,62</t>
+          <t>4,05; 22,93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 14,93</t>
+          <t>-2,43; 16,2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 15,08</t>
+          <t>-1,25; 15,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,75; 15,62</t>
+          <t>1,23; 16,15</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 9,01</t>
+          <t>-7,57; 8,98</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,95; 14,5</t>
+          <t>0,11; 14,04</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,14; 15,96</t>
+          <t>4,2; 16,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 8,79</t>
+          <t>-3,42; 8,81</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,03; 12,86</t>
+          <t>2,3; 12,8</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>6,83; 55,62</t>
+          <t>7,84; 53,73</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 35,23</t>
+          <t>-4,61; 39,38</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 36,32</t>
+          <t>-2,57; 38,75</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,28; 30,21</t>
+          <t>2,11; 31,5</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 17,43</t>
+          <t>-12,42; 17,21</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,18; 28,32</t>
+          <t>0,26; 27,59</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,39; 32,78</t>
+          <t>7,46; 32,76</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 17,71</t>
+          <t>-6,03; 17,58</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>5,47; 25,85</t>
+          <t>4,14; 26,35</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>6,11</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,22</t>
+          <t>3,99</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>5,05</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,46</t>
+          <t>2,14; 5,56</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,8</t>
+          <t>0,33; 3,69</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,07</t>
+          <t>4,47; 7,81</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,0</t>
+          <t>2,11; 5,87</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,64</t>
+          <t>-1,12; 2,82</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,15; 23,52</t>
+          <t>2,39; 5,64</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,16</t>
+          <t>2,66; 5,06</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,7</t>
+          <t>0,09; 2,64</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,71; 14,76</t>
+          <t>3,7; 6,18</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>13,87; 45,45</t>
+          <t>15,37; 45,57</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3,32; 31,33</t>
+          <t>2,37; 30,1</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8,39; 56,92</t>
+          <t>32,82; 65,28</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11,71; 37,81</t>
+          <t>11,97; 36,64</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 16,6</t>
+          <t>-6,33; 17,72</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>18,13; 138,87</t>
+          <t>13,33; 35,13</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,9; 36,11</t>
+          <t>17,16; 35,48</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0,81; 18,68</t>
+          <t>0,5; 18,23</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>23,88; 97,5</t>
+          <t>23,45; 43,09</t>
         </is>
       </c>
     </row>
